--- a/provider_specialty_cprd_V.0.4_omop.xlsx
+++ b/provider_specialty_cprd_V.0.4_omop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/OMOP_Validation study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1ED8615-1082-41F3-85F1-DD4D8090F76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{C1ED8615-1082-41F3-85F1-DD4D8090F76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF604656-AD58-4174-BE6F-0BB18B80BE9E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46870897-BCFD-414C-A471-BD3159C3E0A3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="121">
   <si>
     <t>specialty_concept_id</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Paramedic</t>
   </si>
   <si>
-    <t>Cost per working hour (£47), qualified nurses, assuming 30 min encounter</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>Paramedic Specialist Practitioner</t>
   </si>
   <si>
-    <t>Cost per working hours, Qualified nurse Band 6 (£57), assuming 30 min encounter</t>
-  </si>
-  <si>
     <t>Marriage and Family Therapist</t>
   </si>
   <si>
@@ -399,6 +393,15 @@
   </si>
   <si>
     <t>Average of "Cost per surgery consultation lasting 10 minutes - GP (including direct care staffcosts, without qualification) £42" and "Hospital-based doctors, Consultant medical, Cost per working hour (including qualifications) (143), assumed 30 minutes £71.5"</t>
+  </si>
+  <si>
+    <t>Mean of "Cost per working hour (£47), qualified nurses, assuming 30 min encounter: £23.5" and "Cost per working hours, Qualified nurse Band 6 (£57), assuming 30 min encounter:£28.5"</t>
+  </si>
+  <si>
+    <t>Mean of: "Hospital -based nurses, Band 6, cost per hour (£52), assumed 15 min consultation and 2.5 ratio paid hours: £31.7" and "Hospital based nurses, Staff nurse, midwife (entry level), theatre nurse, Band 5 Cost per hour: £:42"</t>
+  </si>
+  <si>
+    <t>Mean of: "Hospital -based nurses, Band 6, cost per hour (£52), assumed 15 min consultation and 2.5 ratio paid hours:31.72" and "Nurse team leader (learning disabilities), Nurse Specialist (Community), Nurse Specialist (Schools), Nurse Specialist (Special schools), Band 6, Cost per hour face-to-face time, duration of contact 15.5 minutes per surgery consultation based on the 2006/07 UK general practice survey (PSSRU 2015): 26.75" and "</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -806,10 +840,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -821,67 +855,67 @@
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>38004185</v>
+        <v>38003638</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>71.5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>38003696</v>
+        <v>38003781</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>23.5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>38004185</v>
+        <v>38003781</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -895,33 +929,42 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>38004154</v>
+        <v>38004390</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>26.74540816326531</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>38003627</v>
+        <v>38004376</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -930,47 +973,56 @@
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>38003810</v>
+        <v>38003789</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>31.72</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>38003648</v>
+        <v>38003789</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -984,13 +1036,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>38003789</v>
+        <v>38004413</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -999,96 +1051,105 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>31.72</v>
+        <v>26.74540816326531</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>38003781</v>
+        <v>38004446</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>38004154</v>
+        <v>38004446</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>38003731</v>
+        <v>38004169</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>31.72</v>
-      </c>
-      <c r="G12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>38004445</v>
+        <v>38004169</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1102,33 +1163,42 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>38004512</v>
+        <v>38003659</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>38004446</v>
+        <v>38004370</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1137,105 +1207,96 @@
         <v>1</v>
       </c>
       <c r="F15" s="2">
-        <v>42</v>
+        <v>19.196153846153848</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>38003638</v>
+        <v>38003625</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>71.5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>38003794</v>
+        <v>38003648</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2">
-        <v>31.72</v>
-      </c>
-      <c r="G17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>38004371</v>
+        <v>38003807</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>31.72</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>38004499</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1244,16 +1305,16 @@
         <v>1</v>
       </c>
       <c r="F19" s="2">
-        <v>44</v>
+        <v>49.38</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1261,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
         <v>48</v>
@@ -1276,13 +1337,13 @@
         <v>49.38</v>
       </c>
       <c r="G20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1290,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1305,53 +1366,71 @@
         <v>49.38</v>
       </c>
       <c r="G21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>38003625</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>49.38</v>
+      </c>
+      <c r="G22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>38003819</v>
+        <v>38004487</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>19.196153846153848</v>
+      </c>
+      <c r="G23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1362,7 +1441,7 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1376,13 +1455,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>38004154</v>
+        <v>38004185</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1396,13 +1475,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>38004153</v>
+        <v>38004185</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1416,60 +1495,42 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>38003794</v>
+        <v>38004185</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2">
-        <v>26.74540816326531</v>
-      </c>
-      <c r="G27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>38004487</v>
+        <v>38004185</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2">
-        <v>19.196153846153848</v>
-      </c>
-      <c r="G28" t="s">
-        <v>61</v>
-      </c>
-      <c r="H28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1480,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1494,22 +1555,31 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>38004176</v>
+        <v>38003696</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="G30" t="s">
+        <v>118</v>
+      </c>
+      <c r="H30" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1520,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1529,56 +1599,47 @@
         <v>1</v>
       </c>
       <c r="F31" s="2">
-        <v>28.5</v>
+        <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>38003659</v>
+        <v>38003810</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2">
-        <v>53</v>
-      </c>
-      <c r="G32" t="s">
-        <v>69</v>
-      </c>
-      <c r="H32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I32" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>38004145</v>
+        <v>38003819</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1592,33 +1653,42 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>38003731</v>
+        <v>38003819</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>38004512</v>
+        <v>38004145</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1632,33 +1702,42 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>38004169</v>
+        <v>38004056</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>38003789</v>
+        <v>38004512</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1672,42 +1751,33 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>38003716</v>
+        <v>38004512</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>42</v>
-      </c>
-      <c r="G38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" t="s">
-        <v>29</v>
-      </c>
-      <c r="I38" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38004390</v>
+        <v>38004512</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1716,85 +1786,67 @@
         <v>1</v>
       </c>
       <c r="F39" s="2">
-        <v>26.74540816326531</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>38004446</v>
+        <v>38004512</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2">
-        <v>42</v>
-      </c>
-      <c r="G40" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" t="s">
-        <v>37</v>
-      </c>
-      <c r="I40" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>0</v>
+        <v>38004153</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="2">
-        <v>49.38</v>
-      </c>
-      <c r="G41" t="s">
-        <v>119</v>
-      </c>
-      <c r="H41" t="s">
-        <v>37</v>
-      </c>
-      <c r="I41" t="s">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>38003690</v>
+        <v>38004030</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1803,47 +1855,56 @@
         <v>1</v>
       </c>
       <c r="F42" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>38004185</v>
+        <v>38003627</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>38004154</v>
+        <v>38004176</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1857,13 +1918,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>0</v>
+        <v>38003722</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1872,27 +1933,27 @@
         <v>1</v>
       </c>
       <c r="F45" s="2">
-        <v>49.38</v>
+        <v>19.196153846153848</v>
       </c>
       <c r="G45" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="H45" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>38003794</v>
+        <v>38003690</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1901,56 +1962,47 @@
         <v>1</v>
       </c>
       <c r="F46" s="2">
-        <v>31.72</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>38004370</v>
+        <v>38003731</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2">
-        <v>19.196153846153848</v>
-      </c>
-      <c r="G47" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>38004056</v>
+        <v>38003731</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1959,47 +2011,56 @@
         <v>1</v>
       </c>
       <c r="F48" s="2">
-        <v>41</v>
+        <v>36.86</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>38003781</v>
+        <v>38003731</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2">
-        <v>0</v>
+        <v>36.86</v>
+      </c>
+      <c r="G49" t="s">
+        <v>119</v>
+      </c>
+      <c r="H49" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>38003819</v>
+        <v>38003716</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2008,27 +2069,27 @@
         <v>1</v>
       </c>
       <c r="F50" s="2">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I50" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>38003731</v>
+        <v>38003716</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2040,24 +2101,24 @@
         <v>42</v>
       </c>
       <c r="G51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>38004512</v>
+        <v>38004154</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2071,100 +2132,73 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>38003722</v>
+        <v>38004154</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="2">
-        <v>19.196153846153848</v>
-      </c>
-      <c r="G53" t="s">
-        <v>61</v>
-      </c>
-      <c r="H53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I53" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>38004030</v>
+        <v>38004154</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2">
-        <v>41</v>
-      </c>
-      <c r="G54" t="s">
-        <v>16</v>
-      </c>
-      <c r="H54" t="s">
-        <v>10</v>
-      </c>
-      <c r="I54" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>38004413</v>
+        <v>38004154</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2">
-        <v>26.74540816326531</v>
-      </c>
-      <c r="G55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" t="s">
-        <v>29</v>
-      </c>
-      <c r="I55" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>38004185</v>
+        <v>38004154</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2178,33 +2212,42 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>38004169</v>
+        <v>38003760</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
         <v>106</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>19.196153846153848</v>
+      </c>
+      <c r="G57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H57" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>38003760</v>
+        <v>38004499</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2213,27 +2256,27 @@
         <v>1</v>
       </c>
       <c r="F58" s="2">
-        <v>19.196153846153848</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H58" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I58" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>38003807</v>
+        <v>38003794</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2242,47 +2285,56 @@
         <v>1</v>
       </c>
       <c r="F59" s="2">
-        <v>31.72</v>
+        <v>29.23</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="H59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>38004154</v>
+        <v>38003794</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2">
-        <v>0</v>
+        <v>29.23</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I60" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>38003716</v>
+        <v>38003794</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2291,78 +2343,70 @@
         <v>1</v>
       </c>
       <c r="F61" s="2">
-        <v>42</v>
+        <v>29.23</v>
       </c>
       <c r="G61" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I61" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>38004376</v>
+        <v>38004445</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="2">
-        <v>42</v>
-      </c>
-      <c r="G62" t="s">
-        <v>36</v>
-      </c>
-      <c r="H62" t="s">
-        <v>37</v>
-      </c>
-      <c r="I62" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>38004512</v>
+        <v>38004371</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2">
-        <v>42</v>
-      </c>
-      <c r="G63" t="s">
-        <v>36</v>
-      </c>
-      <c r="H63" t="s">
-        <v>37</v>
-      </c>
-      <c r="I63" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I63" xr:uid="{B01908DF-AC8E-4A47-8381-A0A0F45C789A}"/>
+  <autoFilter ref="A1:I63" xr:uid="{B01908DF-AC8E-4A47-8381-A0A0F45C789A}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I63">
+      <sortCondition ref="B1:B63"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>